--- a/data/trans_camb/IP1019-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1019-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,0</t>
+          <t>-3,63; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,0</t>
+          <t>-4,27; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,0</t>
+          <t>-2,23; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,0</t>
+          <t>-2,24; 0,0</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,0</t>
+          <t>-3,15; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,0</t>
+          <t>-3,18; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,0</t>
+          <t>-1,36; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,0</t>
+          <t>-1,52; 0,0</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,5; 0,0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
